--- a/output/pdf_financials_xlsx/AEC.xlsx
+++ b/output/pdf_financials_xlsx/AEC.xlsx
@@ -6145,52 +6145,52 @@
         <v>0.313095</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.135229</v>
       </c>
       <c r="E92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.023842</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.026157</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.028891</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.028891</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.074891</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.105755</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.310178</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.367142</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.511838</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.686698</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>5.939526</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>7.39664</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>7.411788</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>7.605901</v>
       </c>
     </row>
     <row r="93">
@@ -6571,7 +6571,7 @@
         <v>-8.857942</v>
       </c>
       <c r="Q99" s="3" t="n">
-        <v>13.175717</v>
+        <v>-13.175717</v>
       </c>
       <c r="R99" s="3" t="n">
         <v>-11.445652</v>
@@ -6805,16 +6805,16 @@
         <v>-0.114165</v>
       </c>
       <c r="K103" s="3" t="n">
-        <v>0</v>
+        <v>-0.452737</v>
       </c>
       <c r="L103" s="3" t="n">
-        <v>0</v>
+        <v>0.592261</v>
       </c>
       <c r="M103" s="3" t="n">
-        <v>0</v>
+        <v>0.020528</v>
       </c>
       <c r="N103" s="3" t="n">
-        <v>0</v>
+        <v>-0.194766</v>
       </c>
       <c r="O103" s="3" t="n">
         <v>-0.135916</v>
@@ -6823,13 +6823,13 @@
         <v>-0.157743</v>
       </c>
       <c r="Q103" s="3" t="n">
-        <v>0</v>
+        <v>-1.138471</v>
       </c>
       <c r="R103" s="3" t="n">
-        <v>0</v>
+        <v>0.5188430000000001</v>
       </c>
       <c r="S103" s="3" t="n">
-        <v>0</v>
+        <v>-0.463542</v>
       </c>
     </row>
     <row r="104">
@@ -6994,16 +6994,16 @@
         <v>-0.175646</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0.595986</v>
+        <v>0.143249</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0.723838</v>
+        <v>1.316099</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>-0.300904</v>
+        <v>-0.280376</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0.920606</v>
+        <v>0.72584</v>
       </c>
       <c r="O106" s="3" t="n">
         <v>-0.640289</v>
@@ -7012,13 +7012,13 @@
         <v>-0.869819</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>0.476854</v>
+        <v>-0.661617</v>
       </c>
       <c r="R106" s="3" t="n">
-        <v>1.695546</v>
+        <v>2.214389</v>
       </c>
       <c r="S106" s="3" t="n">
-        <v>0.655349</v>
+        <v>0.191807</v>
       </c>
     </row>
     <row r="107">
@@ -9382,7 +9382,11 @@
           <t>Prepaids and deposits 4, 9</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>-</t>
@@ -11176,7 +11180,11 @@
           <t>Warrant reserve 12</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -11808,7 +11816,11 @@
           <t>Prepaids and deposits 9</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -13544,7 +13556,11 @@
           <t>Warrant reserve 12</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -15846,7 +15862,11 @@
           <t>Warrant reserve 8</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -20380,7 +20400,11 @@
           <t>Warrant reserve 6</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
@@ -23074,7 +23098,11 @@
           <t>Warrant reserve 11</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -24638,7 +24666,11 @@
           <t>Warrant reserve 7</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -28036,7 +28068,11 @@
           <t>Warrants reserve 6 – 135,229</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>-</t>
@@ -30019,7 +30055,7 @@
         <v>-8.857942</v>
       </c>
       <c r="T203" s="5" t="n">
-        <v>13.175717</v>
+        <v>-13.175717</v>
       </c>
       <c r="U203" s="5" t="n">
         <v>-11.445652</v>
@@ -30662,7 +30698,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E210" t="inlineStr">
         <is>
           <t>-</t>
@@ -32826,7 +32866,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -39926,7 +39970,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AEC.xlsx
+++ b/output/pdf_financials_xlsx/AEC.xlsx
@@ -986,13 +986,13 @@
         <v>10.559487</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.105948</v>
+        <v>10.029369</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>2.84308</v>
+        <v>9.812828</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>3.091029</v>
+        <v>17.495679</v>
       </c>
     </row>
     <row r="11">
@@ -1110,13 +1110,13 @@
         <v>0</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.637812</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.513693</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>0.670855</v>
       </c>
     </row>
     <row r="13">
@@ -2099,13 +2099,13 @@
         <v>-8.857942</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>13.175717</v>
+        <v>12.537905</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-11.445652</v>
+        <v>-11.959345</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-19.722261</v>
+        <v>-20.393116</v>
       </c>
     </row>
     <row r="28">
@@ -2221,13 +2221,13 @@
         <v>-8.857942</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>13.179536</v>
+        <v>12.541724</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-11.441775</v>
+        <v>-11.955468</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-19.713132</v>
+        <v>-20.383987</v>
       </c>
     </row>
     <row r="30">
@@ -2495,58 +2495,58 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.000685</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.319284</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.319284</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.937496</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.006956</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.038056</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.007492</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.167231</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.283052</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.120771</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.052792</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.022541</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.787225</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>4.849174</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>4.317549</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>2.611281</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>1.350411</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>3.349977</v>
       </c>
     </row>
     <row r="35">
@@ -2617,58 +2617,58 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.000685</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.319284</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.319284</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.937496</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.006956</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.038056</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.007492</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.167231</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.283052</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.120771</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.052792</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.045241</v>
+        <v>0.067782</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.045241</v>
+        <v>1.832466</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.088368</v>
+        <v>4.937542</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.045508</v>
+        <v>4.363057</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.042443</v>
+        <v>2.653724</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.034563</v>
+        <v>1.384974</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0.019884</v>
+        <v>3.369861</v>
       </c>
     </row>
     <row r="37">
@@ -3349,13 +3349,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.000685</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.419284</v>
+        <v>0.1</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.319284</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0</v>
@@ -3364,40 +3364,40 @@
         <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.088404</v>
+        <v>0.050348</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.044915</v>
+        <v>0.037423</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.51324</v>
+        <v>0.346009</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.7432260000000001</v>
+        <v>0.460174</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.7683759999999999</v>
+        <v>0.647605</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.223506</v>
+        <v>0.170714</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.033267</v>
+        <v>0.010726</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>2.08227</v>
+        <v>0.295045</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>5.193867</v>
+        <v>0.344693</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>4.795268</v>
+        <v>0.477719</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>4.195012</v>
+        <v>1.583731</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>2.38585</v>
+        <v>1.035439</v>
       </c>
       <c r="S48" s="3" t="n">
         <v>0</v>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -26676,7 +26676,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -28698,7 +28698,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E191" s="5" t="n">
@@ -31180,7 +31180,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -33270,7 +33274,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -54708,7 +54716,7 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
@@ -55128,7 +55136,7 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
@@ -56460,7 +56468,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
@@ -56780,7 +56788,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
@@ -58684,7 +58692,7 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
@@ -61362,7 +61370,7 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
@@ -62498,7 +62506,7 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
@@ -63854,7 +63862,7 @@
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
@@ -65114,7 +65122,7 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
@@ -65848,7 +65856,7 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
